--- a/data/nzd0545/nzd0545.xlsx
+++ b/data/nzd0545/nzd0545.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R454"/>
+  <dimension ref="A1:R455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27606,6 +27606,66 @@
         <v>260.01</v>
       </c>
       <c r="R454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>454.84</v>
+      </c>
+      <c r="C455" t="n">
+        <v>525.48</v>
+      </c>
+      <c r="D455" t="n">
+        <v>299.49</v>
+      </c>
+      <c r="E455" t="n">
+        <v>283.19</v>
+      </c>
+      <c r="F455" t="n">
+        <v>280.54</v>
+      </c>
+      <c r="G455" t="n">
+        <v>285.3</v>
+      </c>
+      <c r="H455" t="n">
+        <v>283.52</v>
+      </c>
+      <c r="I455" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="J455" t="n">
+        <v>266.29</v>
+      </c>
+      <c r="K455" t="n">
+        <v>270.84</v>
+      </c>
+      <c r="L455" t="n">
+        <v>272.92</v>
+      </c>
+      <c r="M455" t="n">
+        <v>271.11</v>
+      </c>
+      <c r="N455" t="n">
+        <v>267.48</v>
+      </c>
+      <c r="O455" t="n">
+        <v>253.36</v>
+      </c>
+      <c r="P455" t="n">
+        <v>254.46</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>263.82</v>
+      </c>
+      <c r="R455" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27622,7 +27682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B506"/>
+  <dimension ref="A1:B507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32685,6 +32745,16 @@
       </c>
       <c r="B506" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -32853,28 +32923,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08534968019970837</v>
+        <v>-0.08622406873544719</v>
       </c>
       <c r="J2" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K2" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003215191230587222</v>
+        <v>0.003296978483477764</v>
       </c>
       <c r="M2" t="n">
-        <v>7.936632426042062</v>
+        <v>7.923793243994421</v>
       </c>
       <c r="N2" t="n">
-        <v>120.8811874442467</v>
+        <v>120.6215360022386</v>
       </c>
       <c r="O2" t="n">
-        <v>10.99459810289793</v>
+        <v>10.9827836181106</v>
       </c>
       <c r="P2" t="n">
-        <v>459.0423495750397</v>
+        <v>459.0516153430038</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32931,28 +33001,28 @@
         <v>0.0386</v>
       </c>
       <c r="I3" t="n">
-        <v>2.081353871303786</v>
+        <v>2.086731870921532</v>
       </c>
       <c r="J3" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K3" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06042586277060025</v>
+        <v>0.06099527031065455</v>
       </c>
       <c r="M3" t="n">
-        <v>41.25034530425692</v>
+        <v>41.16840023025951</v>
       </c>
       <c r="N3" t="n">
-        <v>3573.813982114712</v>
+        <v>3566.113425374697</v>
       </c>
       <c r="O3" t="n">
-        <v>59.78138491298701</v>
+        <v>59.71694420660435</v>
       </c>
       <c r="P3" t="n">
-        <v>458.7034315790193</v>
+        <v>458.6459757116714</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33009,28 +33079,28 @@
         <v>0.028</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5539531096740121</v>
+        <v>-0.558461001998977</v>
       </c>
       <c r="J4" t="n">
+        <v>454</v>
+      </c>
+      <c r="K4" t="n">
         <v>453</v>
       </c>
-      <c r="K4" t="n">
-        <v>452</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1047680524966164</v>
+        <v>0.1066129730179877</v>
       </c>
       <c r="M4" t="n">
-        <v>9.275075746602093</v>
+        <v>9.281677844170805</v>
       </c>
       <c r="N4" t="n">
-        <v>140.0802040024701</v>
+        <v>139.9927852819761</v>
       </c>
       <c r="O4" t="n">
-        <v>11.83554831862344</v>
+        <v>11.83185468478954</v>
       </c>
       <c r="P4" t="n">
-        <v>324.1680418386394</v>
+        <v>324.2157936208782</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33087,28 +33157,28 @@
         <v>0.0494</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3778599646838343</v>
+        <v>-0.3796021056397459</v>
       </c>
       <c r="J5" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K5" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05596381197447353</v>
+        <v>0.05669964761255331</v>
       </c>
       <c r="M5" t="n">
-        <v>8.65895343350801</v>
+        <v>8.647000089207404</v>
       </c>
       <c r="N5" t="n">
-        <v>128.5170923712489</v>
+        <v>128.2670721154107</v>
       </c>
       <c r="O5" t="n">
-        <v>11.33653793586247</v>
+        <v>11.32550538013252</v>
       </c>
       <c r="P5" t="n">
-        <v>297.0456035893913</v>
+        <v>297.0640572562896</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -33169,28 +33239,28 @@
         <v>0.0721</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4753067847878275</v>
+        <v>-0.4738539207373022</v>
       </c>
       <c r="J6" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K6" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06109071539084165</v>
+        <v>0.06101645528524346</v>
       </c>
       <c r="M6" t="n">
-        <v>10.59658697600763</v>
+        <v>10.57974672351087</v>
       </c>
       <c r="N6" t="n">
-        <v>180.4972097435512</v>
+        <v>180.1128550094472</v>
       </c>
       <c r="O6" t="n">
-        <v>13.43492499955066</v>
+        <v>13.42061306384501</v>
       </c>
       <c r="P6" t="n">
-        <v>289.9339238397641</v>
+        <v>289.9181847992492</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -33251,28 +33321,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1197267421800742</v>
+        <v>-0.11807377866337</v>
       </c>
       <c r="J7" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K7" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005374930228023489</v>
+        <v>0.005252911530676863</v>
       </c>
       <c r="M7" t="n">
-        <v>9.239766615148421</v>
+        <v>9.227043424052425</v>
       </c>
       <c r="N7" t="n">
-        <v>139.3196286974466</v>
+        <v>139.037772294694</v>
       </c>
       <c r="O7" t="n">
-        <v>11.80337361509186</v>
+        <v>11.79142791585031</v>
       </c>
       <c r="P7" t="n">
-        <v>284.8307773693269</v>
+        <v>284.8130251952575</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -33333,28 +33403,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01353837970073044</v>
+        <v>-0.01248743803470578</v>
       </c>
       <c r="J8" t="n">
+        <v>454</v>
+      </c>
+      <c r="K8" t="n">
         <v>453</v>
       </c>
-      <c r="K8" t="n">
-        <v>452</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.000139371307090963</v>
+        <v>0.0001191388886129241</v>
       </c>
       <c r="M8" t="n">
-        <v>6.23396355604992</v>
+        <v>6.225047144970962</v>
       </c>
       <c r="N8" t="n">
-        <v>69.79400906935609</v>
+        <v>69.65188020288774</v>
       </c>
       <c r="O8" t="n">
-        <v>8.354280882838216</v>
+        <v>8.345770198303313</v>
       </c>
       <c r="P8" t="n">
-        <v>281.540160003423</v>
+        <v>281.5289834807663</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33415,28 +33485,28 @@
         <v>0.1322</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03179738657486164</v>
+        <v>-0.03053562007510388</v>
       </c>
       <c r="J9" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K9" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007307483009837412</v>
+        <v>0.000677091978523281</v>
       </c>
       <c r="M9" t="n">
-        <v>6.585424549846138</v>
+        <v>6.577438276083933</v>
       </c>
       <c r="N9" t="n">
-        <v>73.77604022147899</v>
+        <v>73.63087818081372</v>
       </c>
       <c r="O9" t="n">
-        <v>8.589298005161947</v>
+        <v>8.580843675351144</v>
       </c>
       <c r="P9" t="n">
-        <v>274.6244458764685</v>
+        <v>274.6110805867019</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33497,28 +33567,28 @@
         <v>0.0518</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03112130687164279</v>
+        <v>-0.02839006546229289</v>
       </c>
       <c r="J10" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K10" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002175944244786621</v>
+        <v>0.000181917672694043</v>
       </c>
       <c r="M10" t="n">
-        <v>12.60965018789307</v>
+        <v>12.59784527153536</v>
       </c>
       <c r="N10" t="n">
-        <v>234.0413251342842</v>
+        <v>233.6030827443858</v>
       </c>
       <c r="O10" t="n">
-        <v>15.29840923541674</v>
+        <v>15.28407938818645</v>
       </c>
       <c r="P10" t="n">
-        <v>261.0985994357218</v>
+        <v>261.0693753580762</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33575,28 +33645,28 @@
         <v>0.027</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3284714932081911</v>
+        <v>-0.3219308248409867</v>
       </c>
       <c r="J11" t="n">
+        <v>454</v>
+      </c>
+      <c r="K11" t="n">
         <v>453</v>
       </c>
-      <c r="K11" t="n">
-        <v>452</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.02263194659642975</v>
+        <v>0.02182401337094131</v>
       </c>
       <c r="M11" t="n">
-        <v>13.12025231464428</v>
+        <v>13.12466748387139</v>
       </c>
       <c r="N11" t="n">
-        <v>246.700738910088</v>
+        <v>246.6167878845002</v>
       </c>
       <c r="O11" t="n">
-        <v>15.70670999637059</v>
+        <v>15.70403731161195</v>
       </c>
       <c r="P11" t="n">
-        <v>265.0092845301521</v>
+        <v>264.9396303456402</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33653,28 +33723,28 @@
         <v>0.0372</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1549432805375513</v>
+        <v>-0.1479360658977554</v>
       </c>
       <c r="J12" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K12" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002492155020146547</v>
+        <v>0.002281202289693751</v>
       </c>
       <c r="M12" t="n">
-        <v>17.71853417815063</v>
+        <v>17.71032042392202</v>
       </c>
       <c r="N12" t="n">
-        <v>503.3073118218098</v>
+        <v>502.7073007353208</v>
       </c>
       <c r="O12" t="n">
-        <v>22.43451162432135</v>
+        <v>22.42113513485258</v>
       </c>
       <c r="P12" t="n">
-        <v>261.6556247155249</v>
+        <v>261.5803057892421</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33731,28 +33801,28 @@
         <v>0.0323</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6725141051520923</v>
+        <v>-0.6662540448898194</v>
       </c>
       <c r="J13" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K13" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06997719874649544</v>
+        <v>0.06900156763563337</v>
       </c>
       <c r="M13" t="n">
-        <v>13.39129656040665</v>
+        <v>13.38178663658294</v>
       </c>
       <c r="N13" t="n">
-        <v>314.8374002135902</v>
+        <v>314.5519745292509</v>
       </c>
       <c r="O13" t="n">
-        <v>17.7436580279713</v>
+        <v>17.73561317037702</v>
       </c>
       <c r="P13" t="n">
-        <v>275.1513954905429</v>
+        <v>275.0841075535154</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33809,28 +33879,28 @@
         <v>0.035</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.179202831412994</v>
+        <v>-0.1757799887549944</v>
       </c>
       <c r="J14" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K14" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005441161181849674</v>
+        <v>0.005259980454494273</v>
       </c>
       <c r="M14" t="n">
-        <v>13.58771281208526</v>
+        <v>13.57268048477844</v>
       </c>
       <c r="N14" t="n">
-        <v>309.1014940235835</v>
+        <v>308.5428428260756</v>
       </c>
       <c r="O14" t="n">
-        <v>17.58128249086464</v>
+        <v>17.56538763665851</v>
       </c>
       <c r="P14" t="n">
-        <v>264.664052036504</v>
+        <v>264.6274532542859</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33887,28 +33957,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2032451024076186</v>
+        <v>-0.2036012872772096</v>
       </c>
       <c r="J15" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K15" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01750331011880268</v>
+        <v>0.01764819646287175</v>
       </c>
       <c r="M15" t="n">
-        <v>8.911722763161128</v>
+        <v>8.89386702361716</v>
       </c>
       <c r="N15" t="n">
-        <v>123.7282484709359</v>
+        <v>123.4571010992391</v>
       </c>
       <c r="O15" t="n">
-        <v>11.12332002915208</v>
+        <v>11.1111251050125</v>
       </c>
       <c r="P15" t="n">
-        <v>259.5180919086602</v>
+        <v>259.5218648048287</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33965,28 +34035,28 @@
         <v>0.0376</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2521225852565296</v>
+        <v>-0.2528363444252743</v>
       </c>
       <c r="J16" t="n">
+        <v>454</v>
+      </c>
+      <c r="K16" t="n">
         <v>453</v>
       </c>
-      <c r="K16" t="n">
-        <v>452</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.0259608428219763</v>
+        <v>0.02622784667851263</v>
       </c>
       <c r="M16" t="n">
-        <v>8.98829906383779</v>
+        <v>8.971989420951216</v>
       </c>
       <c r="N16" t="n">
-        <v>127.497408746625</v>
+        <v>127.2215212286948</v>
       </c>
       <c r="O16" t="n">
-        <v>11.29147504742516</v>
+        <v>11.27925180269927</v>
       </c>
       <c r="P16" t="n">
-        <v>262.7034574847058</v>
+        <v>262.7110141070749</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34043,28 +34113,28 @@
         <v>0.0414</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3431020831843479</v>
+        <v>-0.3415735295108104</v>
       </c>
       <c r="J17" t="n">
+        <v>454</v>
+      </c>
+      <c r="K17" t="n">
         <v>453</v>
       </c>
-      <c r="K17" t="n">
-        <v>452</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.0503544512447287</v>
+        <v>0.05015164108773285</v>
       </c>
       <c r="M17" t="n">
-        <v>8.608226201984486</v>
+        <v>8.59601135949921</v>
       </c>
       <c r="N17" t="n">
-        <v>118.683571180728</v>
+        <v>118.4470931479487</v>
       </c>
       <c r="O17" t="n">
-        <v>10.89419896920962</v>
+        <v>10.88334016503889</v>
       </c>
       <c r="P17" t="n">
-        <v>269.4654949598984</v>
+        <v>269.4493120464065</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34102,7 +34172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R454"/>
+  <dimension ref="A1:R455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75689,6 +75759,98 @@
         </is>
       </c>
     </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-46.5622929341758,169.5625745945454</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-46.56283327510572,169.56152977982958</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-46.56074453112501,169.5611366085223</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-46.56051430934421,169.56028280049065</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-46.56040506993924,169.55939900721856</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-46.560361506318905,169.55849893443911</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-46.56026044778745,169.5576178960986</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-46.56010586255412,169.55675159173276</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-46.55992006407929,169.55588899131862</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>-46.55986557168578,169.55499044711644</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>-46.55978924453477,169.55409779513204</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>-46.55967853017817,169.55321442412244</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>-46.55955052810997,169.552324383833</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>-46.55934162793664,169.55142169959424</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>-46.55930425935806,169.55049350512556</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>-46.55934289878713,169.5495850290284</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0545/nzd0545.xlsx
+++ b/data/nzd0545/nzd0545.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R455"/>
+  <dimension ref="A1:R456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27621,7 +27621,7 @@
         <v>454.84</v>
       </c>
       <c r="C455" t="n">
-        <v>525.48</v>
+        <v>522.95</v>
       </c>
       <c r="D455" t="n">
         <v>299.49</v>
@@ -27666,6 +27666,66 @@
         <v>263.82</v>
       </c>
       <c r="R455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>452.14</v>
+      </c>
+      <c r="C456" t="n">
+        <v>524.12</v>
+      </c>
+      <c r="D456" t="n">
+        <v>298.53</v>
+      </c>
+      <c r="E456" t="n">
+        <v>285.17</v>
+      </c>
+      <c r="F456" t="n">
+        <v>291.43</v>
+      </c>
+      <c r="G456" t="n">
+        <v>292.39</v>
+      </c>
+      <c r="H456" t="n">
+        <v>288.6</v>
+      </c>
+      <c r="I456" t="n">
+        <v>285.29</v>
+      </c>
+      <c r="J456" t="n">
+        <v>278.61</v>
+      </c>
+      <c r="K456" t="n">
+        <v>278.82</v>
+      </c>
+      <c r="L456" t="n">
+        <v>278.95</v>
+      </c>
+      <c r="M456" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="N456" t="n">
+        <v>267.17</v>
+      </c>
+      <c r="O456" t="n">
+        <v>253.32</v>
+      </c>
+      <c r="P456" t="n">
+        <v>252.65</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>263.36</v>
+      </c>
+      <c r="R456" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27682,7 +27742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B507"/>
+  <dimension ref="A1:B508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32755,6 +32815,16 @@
       </c>
       <c r="B507" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -32923,28 +32993,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08622406873544719</v>
+        <v>-0.08831269736731041</v>
       </c>
       <c r="J2" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K2" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003296978483477764</v>
+        <v>0.003473934592993277</v>
       </c>
       <c r="M2" t="n">
-        <v>7.923793243994421</v>
+        <v>7.917463174434836</v>
       </c>
       <c r="N2" t="n">
-        <v>120.6215360022386</v>
+        <v>120.4016947269944</v>
       </c>
       <c r="O2" t="n">
-        <v>10.9827836181106</v>
+        <v>10.97277060395388</v>
       </c>
       <c r="P2" t="n">
-        <v>459.0516153430038</v>
+        <v>459.0738947424948</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33001,28 +33071,28 @@
         <v>0.0386</v>
       </c>
       <c r="I3" t="n">
-        <v>2.086731870921532</v>
+        <v>2.09019479443346</v>
       </c>
       <c r="J3" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K3" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06099527031065455</v>
+        <v>0.06147203268760171</v>
       </c>
       <c r="M3" t="n">
-        <v>41.16840023025951</v>
+        <v>41.08287143077464</v>
       </c>
       <c r="N3" t="n">
-        <v>3566.113425374697</v>
+        <v>3558.242582654537</v>
       </c>
       <c r="O3" t="n">
-        <v>59.71694420660435</v>
+        <v>59.65100655189765</v>
       </c>
       <c r="P3" t="n">
-        <v>458.6459757116714</v>
+        <v>458.6086539945286</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33079,28 +33149,28 @@
         <v>0.028</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.558461001998977</v>
+        <v>-0.563362314654174</v>
       </c>
       <c r="J4" t="n">
+        <v>455</v>
+      </c>
+      <c r="K4" t="n">
         <v>454</v>
       </c>
-      <c r="K4" t="n">
-        <v>453</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1066129730179877</v>
+        <v>0.1085930930443632</v>
       </c>
       <c r="M4" t="n">
-        <v>9.281677844170805</v>
+        <v>9.29030067193905</v>
       </c>
       <c r="N4" t="n">
-        <v>139.9927852819761</v>
+        <v>139.9423796090419</v>
       </c>
       <c r="O4" t="n">
-        <v>11.83185468478954</v>
+        <v>11.82972440968267</v>
       </c>
       <c r="P4" t="n">
-        <v>324.2157936208782</v>
+        <v>324.2680544925172</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33157,28 +33227,28 @@
         <v>0.0494</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3796021056397459</v>
+        <v>-0.3804233178803099</v>
       </c>
       <c r="J5" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K5" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05669964761255331</v>
+        <v>0.05719698137583584</v>
       </c>
       <c r="M5" t="n">
-        <v>8.647000089207404</v>
+        <v>8.631305482640448</v>
       </c>
       <c r="N5" t="n">
-        <v>128.2670721154107</v>
+        <v>127.9923924754261</v>
       </c>
       <c r="O5" t="n">
-        <v>11.32550538013252</v>
+        <v>11.31337228572569</v>
       </c>
       <c r="P5" t="n">
-        <v>297.0640572562896</v>
+        <v>297.0728130206551</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -33239,28 +33309,28 @@
         <v>0.0721</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4738539207373022</v>
+        <v>-0.4673047036321176</v>
       </c>
       <c r="J6" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K6" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06101645528524346</v>
+        <v>0.05958576645237712</v>
       </c>
       <c r="M6" t="n">
-        <v>10.57974672351087</v>
+        <v>10.5871191045689</v>
       </c>
       <c r="N6" t="n">
-        <v>180.1128550094472</v>
+        <v>180.1511278741541</v>
       </c>
       <c r="O6" t="n">
-        <v>13.42061306384501</v>
+        <v>13.422038886628</v>
       </c>
       <c r="P6" t="n">
-        <v>289.9181847992492</v>
+        <v>289.8467759209857</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -33321,28 +33391,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.11807377866337</v>
+        <v>-0.1131545221457697</v>
       </c>
       <c r="J7" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K7" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005252911530676863</v>
+        <v>0.004841781363243203</v>
       </c>
       <c r="M7" t="n">
-        <v>9.227043424052425</v>
+        <v>9.229611682906176</v>
       </c>
       <c r="N7" t="n">
-        <v>139.037772294694</v>
+        <v>138.9818114055695</v>
       </c>
       <c r="O7" t="n">
-        <v>11.79142791585031</v>
+        <v>11.78905472909383</v>
       </c>
       <c r="P7" t="n">
-        <v>284.8130251952575</v>
+        <v>284.7598499872627</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -33403,28 +33473,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01248743803470578</v>
+        <v>-0.009130856311782983</v>
       </c>
       <c r="J8" t="n">
+        <v>455</v>
+      </c>
+      <c r="K8" t="n">
         <v>454</v>
       </c>
-      <c r="K8" t="n">
-        <v>453</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0001191388886129241</v>
+        <v>6.391157106078182e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.225047144970962</v>
+        <v>6.226533679670368</v>
       </c>
       <c r="N8" t="n">
-        <v>69.65188020288774</v>
+        <v>69.61829450211377</v>
       </c>
       <c r="O8" t="n">
-        <v>8.345770198303313</v>
+        <v>8.343757816602407</v>
       </c>
       <c r="P8" t="n">
-        <v>281.5289834807663</v>
+        <v>281.4930537697608</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33485,28 +33555,28 @@
         <v>0.1322</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03053562007510388</v>
+        <v>-0.02535068716397158</v>
       </c>
       <c r="J9" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K9" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000677091978523281</v>
+        <v>0.0004672772774878542</v>
       </c>
       <c r="M9" t="n">
-        <v>6.577438276083933</v>
+        <v>6.589333620733798</v>
       </c>
       <c r="N9" t="n">
-        <v>73.63087818081372</v>
+        <v>73.75710626305018</v>
       </c>
       <c r="O9" t="n">
-        <v>8.580843675351144</v>
+        <v>8.58819575132345</v>
       </c>
       <c r="P9" t="n">
-        <v>274.6110805867019</v>
+        <v>274.5557988354341</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33567,28 +33637,28 @@
         <v>0.0518</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.02839006546229289</v>
+        <v>-0.02002622120842303</v>
       </c>
       <c r="J10" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K10" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L10" t="n">
-        <v>0.000181917672694043</v>
+        <v>9.069820765428283e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>12.59784527153536</v>
+        <v>12.6187121740248</v>
       </c>
       <c r="N10" t="n">
-        <v>233.6030827443858</v>
+        <v>233.8211896868748</v>
       </c>
       <c r="O10" t="n">
-        <v>15.28407938818645</v>
+        <v>15.29121282589693</v>
       </c>
       <c r="P10" t="n">
-        <v>261.0693753580762</v>
+        <v>260.9793030958237</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33645,28 +33715,28 @@
         <v>0.027</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3219308248409867</v>
+        <v>-0.3117428036254703</v>
       </c>
       <c r="J11" t="n">
+        <v>455</v>
+      </c>
+      <c r="K11" t="n">
         <v>454</v>
       </c>
-      <c r="K11" t="n">
-        <v>453</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.02182401337094131</v>
+        <v>0.02050357416873849</v>
       </c>
       <c r="M11" t="n">
-        <v>13.12466748387139</v>
+        <v>13.14694098731643</v>
       </c>
       <c r="N11" t="n">
-        <v>246.6167878845002</v>
+        <v>247.1730128721341</v>
       </c>
       <c r="O11" t="n">
-        <v>15.70403731161195</v>
+        <v>15.72173695467947</v>
       </c>
       <c r="P11" t="n">
-        <v>264.9396303456402</v>
+        <v>264.8304272822593</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33723,28 +33793,28 @@
         <v>0.0372</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1479360658977554</v>
+        <v>-0.1381447354916708</v>
       </c>
       <c r="J12" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K12" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002281202289693751</v>
+        <v>0.001995858025222952</v>
       </c>
       <c r="M12" t="n">
-        <v>17.71032042392202</v>
+        <v>17.71395187805982</v>
       </c>
       <c r="N12" t="n">
-        <v>502.7073007353208</v>
+        <v>502.5905869151132</v>
       </c>
       <c r="O12" t="n">
-        <v>22.42113513485258</v>
+        <v>22.4185322203554</v>
       </c>
       <c r="P12" t="n">
-        <v>261.5803057892421</v>
+        <v>261.474378524829</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33801,28 +33871,28 @@
         <v>0.0323</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6662540448898194</v>
+        <v>-0.6587878145632975</v>
       </c>
       <c r="J13" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K13" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06900156763563337</v>
+        <v>0.06776843639573449</v>
       </c>
       <c r="M13" t="n">
-        <v>13.38178663658294</v>
+        <v>13.37580349088297</v>
       </c>
       <c r="N13" t="n">
-        <v>314.5519745292509</v>
+        <v>314.4346699285624</v>
       </c>
       <c r="O13" t="n">
-        <v>17.73561317037702</v>
+        <v>17.73230582661382</v>
       </c>
       <c r="P13" t="n">
-        <v>275.0841075535154</v>
+        <v>275.00333432647</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33879,28 +33949,28 @@
         <v>0.035</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1757799887549944</v>
+        <v>-0.172488195567707</v>
       </c>
       <c r="J14" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K14" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005259980454494273</v>
+        <v>0.005089322955037723</v>
       </c>
       <c r="M14" t="n">
-        <v>13.57268048477844</v>
+        <v>13.55692562212191</v>
       </c>
       <c r="N14" t="n">
-        <v>308.5428428260756</v>
+        <v>307.9756392614971</v>
       </c>
       <c r="O14" t="n">
-        <v>17.56538763665851</v>
+        <v>17.54923472010951</v>
       </c>
       <c r="P14" t="n">
-        <v>264.6274532542859</v>
+        <v>264.5920273455091</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33957,28 +34027,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2036012872772096</v>
+        <v>-0.2039612740856874</v>
       </c>
       <c r="J15" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K15" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01764819646287175</v>
+        <v>0.01779645686073139</v>
       </c>
       <c r="M15" t="n">
-        <v>8.89386702361716</v>
+        <v>8.87608139626248</v>
       </c>
       <c r="N15" t="n">
-        <v>123.4571010992391</v>
+        <v>123.1871553597074</v>
       </c>
       <c r="O15" t="n">
-        <v>11.1111251050125</v>
+        <v>11.09897091444551</v>
       </c>
       <c r="P15" t="n">
-        <v>259.5218648048287</v>
+        <v>259.5257029839426</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34035,28 +34105,28 @@
         <v>0.0376</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2528363444252743</v>
+        <v>-0.2543465050875093</v>
       </c>
       <c r="J16" t="n">
+        <v>455</v>
+      </c>
+      <c r="K16" t="n">
         <v>454</v>
       </c>
-      <c r="K16" t="n">
-        <v>453</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.02622784667851263</v>
+        <v>0.02665796329088421</v>
       </c>
       <c r="M16" t="n">
-        <v>8.971989420951216</v>
+        <v>8.959581060267441</v>
       </c>
       <c r="N16" t="n">
-        <v>127.2215212286948</v>
+        <v>126.9657989323668</v>
       </c>
       <c r="O16" t="n">
-        <v>11.27925180269927</v>
+        <v>11.26791014041055</v>
       </c>
       <c r="P16" t="n">
-        <v>262.7110141070749</v>
+        <v>262.7271075332265</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34113,28 +34183,28 @@
         <v>0.0414</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3415735295108104</v>
+        <v>-0.3402294547619337</v>
       </c>
       <c r="J17" t="n">
+        <v>455</v>
+      </c>
+      <c r="K17" t="n">
         <v>454</v>
       </c>
-      <c r="K17" t="n">
-        <v>453</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.05015164108773285</v>
+        <v>0.05000612916583558</v>
       </c>
       <c r="M17" t="n">
-        <v>8.59601135949921</v>
+        <v>8.582938834627409</v>
       </c>
       <c r="N17" t="n">
-        <v>118.4470931479487</v>
+        <v>118.2056048787608</v>
       </c>
       <c r="O17" t="n">
-        <v>10.88334016503889</v>
+        <v>10.8722401039878</v>
       </c>
       <c r="P17" t="n">
-        <v>269.4493120464065</v>
+        <v>269.4349885586782</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34172,7 +34242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R455"/>
+  <dimension ref="A1:R456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75772,7 +75842,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>-46.56283327510572,169.56152977982958</t>
+          <t>-46.56281085125966,169.56153533785292</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -75846,6 +75916,98 @@
         </is>
       </c>
       <c r="R455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>-46.56226900353347,169.56258052562598</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>-46.56282122118062,169.5615327675424</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-46.56073602247103,169.561138717414</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-46.56053185841458,169.56027845073817</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-46.56050158965652,169.55937508253706</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>-46.56042434595032,169.55848335744642</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-46.56030541976833,169.55760629697082</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>-46.5601826903069,169.55673093111088</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>-46.560028971495896,169.55585959979524</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>-46.55993611385735,169.55497140866683</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>-46.55984254885823,169.55408340836865</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>-46.559700806571286,169.55320841151706</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>-46.55954778173189,169.55232507488086</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>-46.5593412713658,169.55142176788908</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>-46.55928807077205,169.55049593369708</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>-46.55933878456615,169.5495856462824</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0545/nzd0545.xlsx
+++ b/data/nzd0545/nzd0545.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R456"/>
+  <dimension ref="A1:R457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27621,7 +27621,7 @@
         <v>454.84</v>
       </c>
       <c r="C455" t="n">
-        <v>522.95</v>
+        <v>525.48</v>
       </c>
       <c r="D455" t="n">
         <v>299.49</v>
@@ -27681,7 +27681,7 @@
         <v>452.14</v>
       </c>
       <c r="C456" t="n">
-        <v>524.12</v>
+        <v>540.48</v>
       </c>
       <c r="D456" t="n">
         <v>298.53</v>
@@ -27728,6 +27728,66 @@
       <c r="R456" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>449.29</v>
+      </c>
+      <c r="C457" t="n">
+        <v>538.28</v>
+      </c>
+      <c r="D457" t="n">
+        <v>304.96</v>
+      </c>
+      <c r="E457" t="n">
+        <v>291.35</v>
+      </c>
+      <c r="F457" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="G457" t="n">
+        <v>296.34</v>
+      </c>
+      <c r="H457" t="n">
+        <v>290.32</v>
+      </c>
+      <c r="I457" t="n">
+        <v>287.87</v>
+      </c>
+      <c r="J457" t="n">
+        <v>287.84</v>
+      </c>
+      <c r="K457" t="n">
+        <v>289.17</v>
+      </c>
+      <c r="L457" t="n">
+        <v>286.01</v>
+      </c>
+      <c r="M457" t="n">
+        <v>282.3</v>
+      </c>
+      <c r="N457" t="n">
+        <v>271.33</v>
+      </c>
+      <c r="O457" t="n">
+        <v>256.71</v>
+      </c>
+      <c r="P457" t="n">
+        <v>259.73</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>272.39</v>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27742,7 +27802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B508"/>
+  <dimension ref="A1:B509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32825,6 +32885,16 @@
       </c>
       <c r="B508" t="n">
         <v>-0.92</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -32993,28 +33063,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08831269736731041</v>
+        <v>-0.09166421064589217</v>
       </c>
       <c r="J2" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K2" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003473934592993277</v>
+        <v>0.003756493742164024</v>
       </c>
       <c r="M2" t="n">
-        <v>7.917463174434836</v>
+        <v>7.917853178687606</v>
       </c>
       <c r="N2" t="n">
-        <v>120.4016947269944</v>
+        <v>120.2570112767388</v>
       </c>
       <c r="O2" t="n">
-        <v>10.97277060395388</v>
+        <v>10.96617578177273</v>
       </c>
       <c r="P2" t="n">
-        <v>459.0738947424948</v>
+        <v>459.1097430331751</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33071,28 +33141,28 @@
         <v>0.0386</v>
       </c>
       <c r="I3" t="n">
-        <v>2.09019479443346</v>
+        <v>2.109734652036048</v>
       </c>
       <c r="J3" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K3" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06147203268760171</v>
+        <v>0.06280464353253823</v>
       </c>
       <c r="M3" t="n">
-        <v>41.08287143077464</v>
+        <v>41.03105139542217</v>
       </c>
       <c r="N3" t="n">
-        <v>3558.242582654537</v>
+        <v>3553.00863745871</v>
       </c>
       <c r="O3" t="n">
-        <v>59.65100655189765</v>
+        <v>59.60711901659658</v>
       </c>
       <c r="P3" t="n">
-        <v>458.6086539945286</v>
+        <v>458.3982825707424</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33149,28 +33219,28 @@
         <v>0.028</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.563362314654174</v>
+        <v>-0.5653057846767886</v>
       </c>
       <c r="J4" t="n">
+        <v>456</v>
+      </c>
+      <c r="K4" t="n">
         <v>455</v>
       </c>
-      <c r="K4" t="n">
-        <v>454</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1085930930443632</v>
+        <v>0.1097210662652052</v>
       </c>
       <c r="M4" t="n">
-        <v>9.29030067193905</v>
+        <v>9.281319111033488</v>
       </c>
       <c r="N4" t="n">
-        <v>139.9423796090419</v>
+        <v>139.6753826110741</v>
       </c>
       <c r="O4" t="n">
-        <v>11.82972440968267</v>
+        <v>11.81843401686848</v>
       </c>
       <c r="P4" t="n">
-        <v>324.2680544925172</v>
+        <v>324.2888332873659</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33227,28 +33297,28 @@
         <v>0.0494</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3804233178803099</v>
+        <v>-0.3784393054361246</v>
       </c>
       <c r="J5" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K5" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05719698137583584</v>
+        <v>0.05688604929710883</v>
       </c>
       <c r="M5" t="n">
-        <v>8.631305482640448</v>
+        <v>8.623638829958672</v>
       </c>
       <c r="N5" t="n">
-        <v>127.9923924754261</v>
+        <v>127.7538975417563</v>
       </c>
       <c r="O5" t="n">
-        <v>11.31337228572569</v>
+        <v>11.30282697123849</v>
       </c>
       <c r="P5" t="n">
-        <v>297.0728130206551</v>
+        <v>297.0516021908604</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -33309,28 +33379,28 @@
         <v>0.0721</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4673047036321176</v>
+        <v>-0.4556595786774559</v>
       </c>
       <c r="J6" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K6" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05958576645237712</v>
+        <v>0.05667499114172625</v>
       </c>
       <c r="M6" t="n">
-        <v>10.5871191045689</v>
+        <v>10.61885282314043</v>
       </c>
       <c r="N6" t="n">
-        <v>180.1511278741541</v>
+        <v>181.1481991089393</v>
       </c>
       <c r="O6" t="n">
-        <v>13.422038886628</v>
+        <v>13.45913069662894</v>
       </c>
       <c r="P6" t="n">
-        <v>289.8467759209857</v>
+        <v>289.7194640135456</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -33391,28 +33461,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1131545221457697</v>
+        <v>-0.1064602238467637</v>
       </c>
       <c r="J7" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K7" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004841781363243203</v>
+        <v>0.004295295323684889</v>
       </c>
       <c r="M7" t="n">
-        <v>9.229611682906176</v>
+        <v>9.240378133277174</v>
       </c>
       <c r="N7" t="n">
-        <v>138.9818114055695</v>
+        <v>139.1429054855439</v>
       </c>
       <c r="O7" t="n">
-        <v>11.78905472909383</v>
+        <v>11.79588510818683</v>
       </c>
       <c r="P7" t="n">
-        <v>284.7598499872627</v>
+        <v>284.6872925623437</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -33473,28 +33543,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.009130856311782983</v>
+        <v>-0.00502261309052977</v>
       </c>
       <c r="J8" t="n">
+        <v>456</v>
+      </c>
+      <c r="K8" t="n">
         <v>455</v>
       </c>
-      <c r="K8" t="n">
-        <v>454</v>
-      </c>
       <c r="L8" t="n">
-        <v>6.391157106078182e-05</v>
+        <v>1.938622969210879e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.226533679670368</v>
+        <v>6.23137173991684</v>
       </c>
       <c r="N8" t="n">
-        <v>69.61829450211377</v>
+        <v>69.64485329364858</v>
       </c>
       <c r="O8" t="n">
-        <v>8.343757816602407</v>
+        <v>8.345349201420428</v>
       </c>
       <c r="P8" t="n">
-        <v>281.4930537697608</v>
+        <v>281.4489594401384</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33555,28 +33625,28 @@
         <v>0.1322</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02535068716397158</v>
+        <v>-0.01904431649364502</v>
       </c>
       <c r="J9" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K9" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004672772774878542</v>
+        <v>0.0002635608981523818</v>
       </c>
       <c r="M9" t="n">
-        <v>6.589333620733798</v>
+        <v>6.606672859979049</v>
       </c>
       <c r="N9" t="n">
-        <v>73.75710626305018</v>
+        <v>74.02162466610734</v>
       </c>
       <c r="O9" t="n">
-        <v>8.58819575132345</v>
+        <v>8.603582083417775</v>
       </c>
       <c r="P9" t="n">
-        <v>274.5557988354341</v>
+        <v>274.4883782124926</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33637,28 +33707,28 @@
         <v>0.0518</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.02002622120842303</v>
+        <v>-0.007518882163264485</v>
       </c>
       <c r="J10" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K10" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L10" t="n">
-        <v>9.069820765428283e-05</v>
+        <v>1.276103244052251e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>12.6187121740248</v>
+        <v>12.6643690479101</v>
       </c>
       <c r="N10" t="n">
-        <v>233.8211896868748</v>
+        <v>234.9476042128823</v>
       </c>
       <c r="O10" t="n">
-        <v>15.29121282589693</v>
+        <v>15.32800065934505</v>
       </c>
       <c r="P10" t="n">
-        <v>260.9793030958237</v>
+        <v>260.8442482330482</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33715,28 +33785,28 @@
         <v>0.027</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3117428036254703</v>
+        <v>-0.2969324433206509</v>
       </c>
       <c r="J11" t="n">
+        <v>456</v>
+      </c>
+      <c r="K11" t="n">
         <v>455</v>
       </c>
-      <c r="K11" t="n">
-        <v>454</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.02050357416873849</v>
+        <v>0.01855766801457837</v>
       </c>
       <c r="M11" t="n">
-        <v>13.14694098731643</v>
+        <v>13.19186864648208</v>
       </c>
       <c r="N11" t="n">
-        <v>247.1730128721341</v>
+        <v>248.9538886772874</v>
       </c>
       <c r="O11" t="n">
-        <v>15.72173695467947</v>
+        <v>15.77827267723839</v>
       </c>
       <c r="P11" t="n">
-        <v>264.8304272822593</v>
+        <v>264.6712514242521</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33793,28 +33863,28 @@
         <v>0.0372</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1381447354916708</v>
+        <v>-0.1251880668898406</v>
       </c>
       <c r="J12" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K12" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001995858025222952</v>
+        <v>0.001642168887450168</v>
       </c>
       <c r="M12" t="n">
-        <v>17.71395187805982</v>
+        <v>17.73111557643563</v>
       </c>
       <c r="N12" t="n">
-        <v>502.5905869151132</v>
+        <v>503.2284847853217</v>
       </c>
       <c r="O12" t="n">
-        <v>22.4185322203554</v>
+        <v>22.43275473020025</v>
       </c>
       <c r="P12" t="n">
-        <v>261.474378524829</v>
+        <v>261.3338318121093</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33871,28 +33941,28 @@
         <v>0.0323</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6587878145632975</v>
+        <v>-0.6473843427633313</v>
       </c>
       <c r="J13" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K13" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06776843639573449</v>
+        <v>0.06563995925791899</v>
       </c>
       <c r="M13" t="n">
-        <v>13.37580349088297</v>
+        <v>13.38207901605491</v>
       </c>
       <c r="N13" t="n">
-        <v>314.4346699285624</v>
+        <v>315.0948301474351</v>
       </c>
       <c r="O13" t="n">
-        <v>17.73230582661382</v>
+        <v>17.75091068501656</v>
       </c>
       <c r="P13" t="n">
-        <v>275.00333432647</v>
+        <v>274.8796358261588</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33949,28 +34019,28 @@
         <v>0.035</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.172488195567707</v>
+        <v>-0.1673197268186472</v>
       </c>
       <c r="J14" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K14" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005089322955037723</v>
+        <v>0.004810035567399562</v>
       </c>
       <c r="M14" t="n">
-        <v>13.55692562212191</v>
+        <v>13.54918195742789</v>
       </c>
       <c r="N14" t="n">
-        <v>307.9756392614971</v>
+        <v>307.5781719699027</v>
       </c>
       <c r="O14" t="n">
-        <v>17.54923472010951</v>
+        <v>17.53790671573728</v>
       </c>
       <c r="P14" t="n">
-        <v>264.5920273455091</v>
+        <v>264.536255847026</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34027,28 +34097,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2039612740856874</v>
+        <v>-0.202782986346415</v>
       </c>
       <c r="J15" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K15" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01779645686073139</v>
+        <v>0.01767969965853833</v>
       </c>
       <c r="M15" t="n">
-        <v>8.87608139626248</v>
+        <v>8.862284892308523</v>
       </c>
       <c r="N15" t="n">
-        <v>123.1871553597074</v>
+        <v>122.9318888410454</v>
       </c>
       <c r="O15" t="n">
-        <v>11.09897091444551</v>
+        <v>11.08746539300328</v>
       </c>
       <c r="P15" t="n">
-        <v>259.5257029839426</v>
+        <v>259.5131060565593</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34105,28 +34175,28 @@
         <v>0.0376</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2543465050875093</v>
+        <v>-0.2526467262481643</v>
       </c>
       <c r="J16" t="n">
+        <v>456</v>
+      </c>
+      <c r="K16" t="n">
         <v>455</v>
       </c>
-      <c r="K16" t="n">
-        <v>454</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.02665796329088421</v>
+        <v>0.02643437129071458</v>
       </c>
       <c r="M16" t="n">
-        <v>8.959581060267441</v>
+        <v>8.948141068663903</v>
       </c>
       <c r="N16" t="n">
-        <v>126.9657989323668</v>
+        <v>126.7178029380963</v>
       </c>
       <c r="O16" t="n">
-        <v>11.26791014041055</v>
+        <v>11.25690023665913</v>
       </c>
       <c r="P16" t="n">
-        <v>262.7271075332265</v>
+        <v>262.708944159146</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34183,28 +34253,28 @@
         <v>0.0414</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3402294547619337</v>
+        <v>-0.3348167722201452</v>
       </c>
       <c r="J17" t="n">
+        <v>456</v>
+      </c>
+      <c r="K17" t="n">
         <v>455</v>
       </c>
-      <c r="K17" t="n">
-        <v>454</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.05000612916583558</v>
+        <v>0.04861224876425585</v>
       </c>
       <c r="M17" t="n">
-        <v>8.582938834627409</v>
+        <v>8.587581733017847</v>
       </c>
       <c r="N17" t="n">
-        <v>118.2056048787608</v>
+        <v>118.2606581599736</v>
       </c>
       <c r="O17" t="n">
-        <v>10.8722401039878</v>
+        <v>10.87477163714133</v>
       </c>
       <c r="P17" t="n">
-        <v>269.4349885586782</v>
+        <v>269.3771501061042</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34242,7 +34312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R456"/>
+  <dimension ref="A1:R457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75842,7 +75912,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>-46.56281085125966,169.56153533785292</t>
+          <t>-46.56283327510572,169.56152977982958</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -75934,7 +76004,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>-46.56282122118062,169.5615327675424</t>
+          <t>-46.562966222799965,169.56149682701738</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -76010,6 +76080,98 @@
       <c r="R456" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>-46.56224374341044,169.56258678620475</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>-46.56294672380582,169.5615016601077</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>-46.560793012725014,169.56112459221922</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-46.560586632783874,169.56026487421792</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-46.56059970473215,169.5593507623095</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>-46.560459355334345,169.5584746791327</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-46.56032064650158,169.55760236970227</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>-46.560205499926205,169.55672479710483</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>-46.560110563651314,169.55583757992443</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>-46.56002760651568,169.55494671585967</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>-46.559904958228195,169.55406656412526</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>-46.55977744796739,169.5531877252499</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>-46.55958463635341,169.55231580145795</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>-46.55937149074487,169.55141597989982</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>-46.55935139408006,169.5504864340815</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>-46.559419548511215,169.54957352929796</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0545/nzd0545.xlsx
+++ b/data/nzd0545/nzd0545.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R457"/>
+  <dimension ref="A1:R462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27750,7 +27750,7 @@
         <v>291.35</v>
       </c>
       <c r="F457" t="n">
-        <v>302.5</v>
+        <v>297.69</v>
       </c>
       <c r="G457" t="n">
         <v>296.34</v>
@@ -27762,16 +27762,16 @@
         <v>287.87</v>
       </c>
       <c r="J457" t="n">
-        <v>287.84</v>
+        <v>284.11</v>
       </c>
       <c r="K457" t="n">
-        <v>289.17</v>
+        <v>282.99</v>
       </c>
       <c r="L457" t="n">
-        <v>286.01</v>
+        <v>280.39</v>
       </c>
       <c r="M457" t="n">
-        <v>282.3</v>
+        <v>276.37</v>
       </c>
       <c r="N457" t="n">
         <v>271.33</v>
@@ -27786,6 +27786,306 @@
         <v>272.39</v>
       </c>
       <c r="R457" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>454.15</v>
+      </c>
+      <c r="C458" t="n">
+        <v>538.28</v>
+      </c>
+      <c r="D458" t="n">
+        <v>304.96</v>
+      </c>
+      <c r="E458" t="n">
+        <v>292.74</v>
+      </c>
+      <c r="F458" t="n">
+        <v>296.85</v>
+      </c>
+      <c r="G458" t="n">
+        <v>297.1</v>
+      </c>
+      <c r="H458" t="n">
+        <v>291.26</v>
+      </c>
+      <c r="I458" t="n">
+        <v>288.66</v>
+      </c>
+      <c r="J458" t="n">
+        <v>285.03</v>
+      </c>
+      <c r="K458" t="n">
+        <v>281.83</v>
+      </c>
+      <c r="L458" t="n">
+        <v>277.1</v>
+      </c>
+      <c r="M458" t="n">
+        <v>276.21</v>
+      </c>
+      <c r="N458" t="n">
+        <v>271.33</v>
+      </c>
+      <c r="O458" t="n">
+        <v>256.71</v>
+      </c>
+      <c r="P458" t="n">
+        <v>259.73</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>272.39</v>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>456.72</v>
+      </c>
+      <c r="C459" t="n">
+        <v>536.49</v>
+      </c>
+      <c r="D459" t="n">
+        <v>315.38</v>
+      </c>
+      <c r="E459" t="n">
+        <v>292.44</v>
+      </c>
+      <c r="F459" t="n">
+        <v>294.06</v>
+      </c>
+      <c r="G459" t="n">
+        <v>295.61</v>
+      </c>
+      <c r="H459" t="n">
+        <v>290.76</v>
+      </c>
+      <c r="I459" t="n">
+        <v>286.76</v>
+      </c>
+      <c r="J459" t="n">
+        <v>284.89</v>
+      </c>
+      <c r="K459" t="n">
+        <v>278.09</v>
+      </c>
+      <c r="L459" t="n">
+        <v>275.19</v>
+      </c>
+      <c r="M459" t="n">
+        <v>274.02</v>
+      </c>
+      <c r="N459" t="n">
+        <v>271.35</v>
+      </c>
+      <c r="O459" t="n">
+        <v>254.56</v>
+      </c>
+      <c r="P459" t="n">
+        <v>262.67</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>274.55</v>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:41+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>454.63</v>
+      </c>
+      <c r="C460" t="n">
+        <v>528.9299999999999</v>
+      </c>
+      <c r="D460" t="n">
+        <v>317</v>
+      </c>
+      <c r="E460" t="n">
+        <v>289.54</v>
+      </c>
+      <c r="F460" t="n">
+        <v>289.39</v>
+      </c>
+      <c r="G460" t="n">
+        <v>292.41</v>
+      </c>
+      <c r="H460" t="n">
+        <v>288.65</v>
+      </c>
+      <c r="I460" t="n">
+        <v>283.73</v>
+      </c>
+      <c r="J460" t="n">
+        <v>281.06</v>
+      </c>
+      <c r="K460" t="n">
+        <v>275.18</v>
+      </c>
+      <c r="L460" t="n">
+        <v>275.02</v>
+      </c>
+      <c r="M460" t="n">
+        <v>273.47</v>
+      </c>
+      <c r="N460" t="n">
+        <v>271.52</v>
+      </c>
+      <c r="O460" t="n">
+        <v>254.89</v>
+      </c>
+      <c r="P460" t="n">
+        <v>262.01</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>453.78</v>
+      </c>
+      <c r="C461" t="n">
+        <v>518.45</v>
+      </c>
+      <c r="D461" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="E461" t="n">
+        <v>292.24</v>
+      </c>
+      <c r="F461" t="n">
+        <v>285.13</v>
+      </c>
+      <c r="G461" t="n">
+        <v>289.1</v>
+      </c>
+      <c r="H461" t="n">
+        <v>286.51</v>
+      </c>
+      <c r="I461" t="n">
+        <v>279.2</v>
+      </c>
+      <c r="J461" t="n">
+        <v>280.79</v>
+      </c>
+      <c r="K461" t="n">
+        <v>274.83</v>
+      </c>
+      <c r="L461" t="n">
+        <v>276.35</v>
+      </c>
+      <c r="M461" t="n">
+        <v>275.74</v>
+      </c>
+      <c r="N461" t="n">
+        <v>274.58</v>
+      </c>
+      <c r="O461" t="n">
+        <v>257</v>
+      </c>
+      <c r="P461" t="n">
+        <v>262.57</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>272.02</v>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>448.98</v>
+      </c>
+      <c r="C462" t="n">
+        <v>514.0599999999999</v>
+      </c>
+      <c r="D462" t="n">
+        <v>327</v>
+      </c>
+      <c r="E462" t="n">
+        <v>291.89</v>
+      </c>
+      <c r="F462" t="n">
+        <v>281.01</v>
+      </c>
+      <c r="G462" t="n">
+        <v>285.98</v>
+      </c>
+      <c r="H462" t="n">
+        <v>283.95</v>
+      </c>
+      <c r="I462" t="n">
+        <v>275.93</v>
+      </c>
+      <c r="J462" t="n">
+        <v>278.51</v>
+      </c>
+      <c r="K462" t="n">
+        <v>273.15</v>
+      </c>
+      <c r="L462" t="n">
+        <v>276.1</v>
+      </c>
+      <c r="M462" t="n">
+        <v>276.25</v>
+      </c>
+      <c r="N462" t="n">
+        <v>276.28</v>
+      </c>
+      <c r="O462" t="n">
+        <v>258.77</v>
+      </c>
+      <c r="P462" t="n">
+        <v>262.97</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>271.41</v>
+      </c>
+      <c r="R462" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27802,7 +28102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B509"/>
+  <dimension ref="A1:B514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32895,6 +33195,56 @@
       </c>
       <c r="B509" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -33063,28 +33413,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09166421064589217</v>
+        <v>-0.09827595283100453</v>
       </c>
       <c r="J2" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K2" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003756493742164024</v>
+        <v>0.004416901788896865</v>
       </c>
       <c r="M2" t="n">
-        <v>7.917853178687606</v>
+        <v>7.866866605894202</v>
       </c>
       <c r="N2" t="n">
-        <v>120.2570112767388</v>
+        <v>119.110149918712</v>
       </c>
       <c r="O2" t="n">
-        <v>10.96617578177273</v>
+        <v>10.9137596601131</v>
       </c>
       <c r="P2" t="n">
-        <v>459.1097430331751</v>
+        <v>459.1807965742273</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33141,28 +33491,28 @@
         <v>0.0386</v>
       </c>
       <c r="I3" t="n">
-        <v>2.109734652036048</v>
+        <v>2.137431521125991</v>
       </c>
       <c r="J3" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K3" t="n">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06280464353253823</v>
+        <v>0.06582314943517853</v>
       </c>
       <c r="M3" t="n">
-        <v>41.03105139542217</v>
+        <v>40.64119203132296</v>
       </c>
       <c r="N3" t="n">
-        <v>3553.00863745871</v>
+        <v>3516.481739880146</v>
       </c>
       <c r="O3" t="n">
-        <v>59.60711901659658</v>
+        <v>59.29993035308006</v>
       </c>
       <c r="P3" t="n">
-        <v>458.3982825707424</v>
+        <v>458.0986402619718</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33219,28 +33569,28 @@
         <v>0.028</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5653057846767886</v>
+        <v>-0.5453025876265697</v>
       </c>
       <c r="J4" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K4" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1097210662652052</v>
+        <v>0.1040997760123759</v>
       </c>
       <c r="M4" t="n">
-        <v>9.281319111033488</v>
+        <v>9.277128614856622</v>
       </c>
       <c r="N4" t="n">
-        <v>139.6753826110741</v>
+        <v>139.7686030738319</v>
       </c>
       <c r="O4" t="n">
-        <v>11.81843401686848</v>
+        <v>11.82237721754098</v>
       </c>
       <c r="P4" t="n">
-        <v>324.2888332873659</v>
+        <v>324.073889203211</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33297,28 +33647,28 @@
         <v>0.0494</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3784393054361246</v>
+        <v>-0.3678462399541984</v>
       </c>
       <c r="J5" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K5" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05688604929710883</v>
+        <v>0.05508727281608816</v>
       </c>
       <c r="M5" t="n">
-        <v>8.623638829958672</v>
+        <v>8.589174594495386</v>
       </c>
       <c r="N5" t="n">
-        <v>127.7538975417563</v>
+        <v>126.6265444793412</v>
       </c>
       <c r="O5" t="n">
-        <v>11.30282697123849</v>
+        <v>11.25284606130117</v>
       </c>
       <c r="P5" t="n">
-        <v>297.0516021908604</v>
+        <v>296.9378921094058</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -33379,28 +33729,28 @@
         <v>0.0721</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4556595786774559</v>
+        <v>-0.4313172255007008</v>
       </c>
       <c r="J6" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K6" t="n">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05667499114172625</v>
+        <v>0.05193421901805007</v>
       </c>
       <c r="M6" t="n">
-        <v>10.61885282314043</v>
+        <v>10.61565332385541</v>
       </c>
       <c r="N6" t="n">
-        <v>181.1481991089393</v>
+        <v>180.5087863718879</v>
       </c>
       <c r="O6" t="n">
-        <v>13.45913069662894</v>
+        <v>13.43535583346745</v>
       </c>
       <c r="P6" t="n">
-        <v>289.7194640135456</v>
+        <v>289.4523151423577</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -33461,28 +33811,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1064602238467637</v>
+        <v>-0.08371940274674243</v>
       </c>
       <c r="J7" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K7" t="n">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004295295323684889</v>
+        <v>0.00270242558860434</v>
       </c>
       <c r="M7" t="n">
-        <v>9.240378133277174</v>
+        <v>9.245359822320657</v>
       </c>
       <c r="N7" t="n">
-        <v>139.1429054855439</v>
+        <v>138.8998718119863</v>
       </c>
       <c r="O7" t="n">
-        <v>11.79588510818683</v>
+        <v>11.78557897652832</v>
       </c>
       <c r="P7" t="n">
-        <v>284.6872925623437</v>
+        <v>284.4399184610237</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -33543,28 +33893,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.00502261309052977</v>
+        <v>0.01019613338832565</v>
       </c>
       <c r="J8" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K8" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L8" t="n">
-        <v>1.938622969210879e-05</v>
+        <v>8.121131503691092e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.23137173991684</v>
+        <v>6.231707854587031</v>
       </c>
       <c r="N8" t="n">
-        <v>69.64485329364858</v>
+        <v>69.46902452979215</v>
       </c>
       <c r="O8" t="n">
-        <v>8.345349201420428</v>
+        <v>8.334808007974278</v>
       </c>
       <c r="P8" t="n">
-        <v>281.4489594401384</v>
+        <v>281.2850185610583</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33625,28 +33975,28 @@
         <v>0.1322</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01904431649364502</v>
+        <v>0.0004041849670550115</v>
       </c>
       <c r="J9" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K9" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002635608981523818</v>
+        <v>1.199823710384962e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>6.606672859979049</v>
+        <v>6.632333207151345</v>
       </c>
       <c r="N9" t="n">
-        <v>74.02162466610734</v>
+        <v>74.28386759485163</v>
       </c>
       <c r="O9" t="n">
-        <v>8.603582083417775</v>
+        <v>8.618808942937047</v>
       </c>
       <c r="P9" t="n">
-        <v>274.4883782124926</v>
+        <v>274.2797277135003</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33707,28 +34057,28 @@
         <v>0.0518</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.007518882163264485</v>
+        <v>0.03839795989962191</v>
       </c>
       <c r="J10" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K10" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="L10" t="n">
-        <v>1.276103244052251e-05</v>
+        <v>0.0003346478814647558</v>
       </c>
       <c r="M10" t="n">
-        <v>12.6643690479101</v>
+        <v>12.79504102683305</v>
       </c>
       <c r="N10" t="n">
-        <v>234.9476042128823</v>
+        <v>236.8749872600667</v>
       </c>
       <c r="O10" t="n">
-        <v>15.32800065934505</v>
+        <v>15.39074355773842</v>
       </c>
       <c r="P10" t="n">
-        <v>260.8442482330482</v>
+        <v>260.3464269696788</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33785,28 +34135,28 @@
         <v>0.027</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2969324433206509</v>
+        <v>-0.2557521147937718</v>
       </c>
       <c r="J11" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K11" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01855766801457837</v>
+        <v>0.01398261346748531</v>
       </c>
       <c r="M11" t="n">
-        <v>13.19186864648208</v>
+        <v>13.25361339112683</v>
       </c>
       <c r="N11" t="n">
-        <v>248.9538886772874</v>
+        <v>249.721046243708</v>
       </c>
       <c r="O11" t="n">
-        <v>15.77827267723839</v>
+        <v>15.80256454641803</v>
       </c>
       <c r="P11" t="n">
-        <v>264.6712514242521</v>
+        <v>264.2268206692582</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33863,28 +34213,28 @@
         <v>0.0372</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1251880668898406</v>
+        <v>-0.0875290228297067</v>
       </c>
       <c r="J12" t="n">
+        <v>461</v>
+      </c>
+      <c r="K12" t="n">
         <v>456</v>
       </c>
-      <c r="K12" t="n">
-        <v>451</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.001642168887450168</v>
+        <v>0.0008191350778555817</v>
       </c>
       <c r="M12" t="n">
-        <v>17.73111557643563</v>
+        <v>17.69782182191966</v>
       </c>
       <c r="N12" t="n">
-        <v>503.2284847853217</v>
+        <v>500.5238559141036</v>
       </c>
       <c r="O12" t="n">
-        <v>22.43275473020025</v>
+        <v>22.37239048278265</v>
       </c>
       <c r="P12" t="n">
-        <v>261.3338318121093</v>
+        <v>260.9235733738494</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33941,28 +34291,28 @@
         <v>0.0323</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6473843427633313</v>
+        <v>-0.6107759596681004</v>
       </c>
       <c r="J13" t="n">
+        <v>461</v>
+      </c>
+      <c r="K13" t="n">
         <v>456</v>
       </c>
-      <c r="K13" t="n">
-        <v>451</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.06563995925791899</v>
+        <v>0.05975865060069785</v>
       </c>
       <c r="M13" t="n">
-        <v>13.38207901605491</v>
+        <v>13.35249724066434</v>
       </c>
       <c r="N13" t="n">
-        <v>315.0948301474351</v>
+        <v>314.3652051214377</v>
       </c>
       <c r="O13" t="n">
-        <v>17.75091068501656</v>
+        <v>17.7303470107451</v>
       </c>
       <c r="P13" t="n">
-        <v>274.8796358261588</v>
+        <v>274.4808028215086</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34019,28 +34369,28 @@
         <v>0.035</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1673197268186472</v>
+        <v>-0.1385704603564162</v>
       </c>
       <c r="J14" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K14" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="L14" t="n">
-        <v>0.004810035567399562</v>
+        <v>0.003367286128370228</v>
       </c>
       <c r="M14" t="n">
-        <v>13.54918195742789</v>
+        <v>13.5232033035407</v>
       </c>
       <c r="N14" t="n">
-        <v>307.5781719699027</v>
+        <v>306.0351109553362</v>
       </c>
       <c r="O14" t="n">
-        <v>17.53790671573728</v>
+        <v>17.49385923560997</v>
       </c>
       <c r="P14" t="n">
-        <v>264.536255847026</v>
+        <v>264.2247336281575</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34097,28 +34447,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.202782986346415</v>
+        <v>-0.1977524081102274</v>
       </c>
       <c r="J15" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K15" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01767969965853833</v>
+        <v>0.01723180079366415</v>
       </c>
       <c r="M15" t="n">
-        <v>8.862284892308523</v>
+        <v>8.789884677946839</v>
       </c>
       <c r="N15" t="n">
-        <v>122.9318888410454</v>
+        <v>121.6790129996455</v>
       </c>
       <c r="O15" t="n">
-        <v>11.08746539300328</v>
+        <v>11.03082104830123</v>
       </c>
       <c r="P15" t="n">
-        <v>259.5131060565593</v>
+        <v>259.4590809679796</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34175,28 +34525,28 @@
         <v>0.0376</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2526467262481643</v>
+        <v>-0.239413127278337</v>
       </c>
       <c r="J16" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K16" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02643437129071458</v>
+        <v>0.02430907244598945</v>
       </c>
       <c r="M16" t="n">
-        <v>8.948141068663903</v>
+        <v>8.913816710831073</v>
       </c>
       <c r="N16" t="n">
-        <v>126.7178029380963</v>
+        <v>125.7369514584613</v>
       </c>
       <c r="O16" t="n">
-        <v>11.25690023665913</v>
+        <v>11.21324892519832</v>
       </c>
       <c r="P16" t="n">
-        <v>262.708944159146</v>
+        <v>262.5669339568169</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34253,28 +34603,28 @@
         <v>0.0414</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3348167722201452</v>
+        <v>-0.3073089803969348</v>
       </c>
       <c r="J17" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K17" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04861224876425585</v>
+        <v>0.04169039933363716</v>
       </c>
       <c r="M17" t="n">
-        <v>8.587581733017847</v>
+        <v>8.611865167187618</v>
       </c>
       <c r="N17" t="n">
-        <v>118.2606581599736</v>
+        <v>118.6433541278075</v>
       </c>
       <c r="O17" t="n">
-        <v>10.87477163714133</v>
+        <v>10.89235301153096</v>
       </c>
       <c r="P17" t="n">
-        <v>269.3771501061042</v>
+        <v>269.0820296233964</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34312,7 +34662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R457"/>
+  <dimension ref="A1:R462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76111,7 +76461,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>-46.56059970473215,169.5593507623095</t>
+          <t>-46.560557072979506,169.5593613296471</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -76131,22 +76481,22 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>-46.560110563651314,169.55583757992443</t>
+          <t>-46.56007759087428,169.55584647853755</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>-46.56002760651568,169.55494671585967</t>
+          <t>-46.55997297611786,169.55496145998163</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>-46.559904958228195,169.55406656412526</t>
+          <t>-46.55985527824848,169.55407997271908</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>-46.55977744796739,169.5531877252499</t>
+          <t>-46.55972502772827,169.5532018739955</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -76170,6 +76520,466 @@
         </is>
       </c>
       <c r="R457" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>-46.56228681856726,169.56257611026655</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>-46.56294672380582,169.5615016601077</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>-46.560793012725014,169.56112459221922</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-46.560598952584996,169.5602618205951</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-46.56054962793314,169.5593631750846</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>-46.56046609131697,169.55847300937978</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-46.56032896808825,169.55760022340328</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>-46.56021248426689,169.55672291886157</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>-46.560085723570054,169.55584428370645</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>-46.55996272186808,169.55496422748305</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>-46.559826195127464,169.55408782222145</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>-46.55972361335415,169.55320225574877</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>-46.55958463635341,169.55231580145795</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>-46.55937149074487,169.55141597989982</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>-46.55935139408006,169.5504864340815</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>-46.559419548511215,169.54957352929796</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-46.56230959699312,169.56257046475253</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-46.56293085871487,169.56150559248292</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-46.56088536706486,169.56110170186477</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-46.56059629363513,169.5602624796505</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-46.56052489974304,169.55936930456951</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-46.56045288524574,169.55847628297388</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-46.56032454171237,169.55760136505177</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>-46.56019568648541,169.55672743615466</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>-46.560084485985925,169.55584461770255</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>-46.55992966075164,169.55497315028165</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>-46.55980931100514,169.55409237922308</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>-46.55970425410827,169.5532074809943</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>-46.55958481353908,169.55231575687415</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>-46.55935232506204,169.55141965074932</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>-46.559377689351464,169.55048248931817</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>-46.55943886746104,169.54957063087676</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:41+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>-46.56229107290364,169.56257505585188</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>-46.56286385307683,169.56152220069865</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>-46.56089972541642,169.56109814308786</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-46.56057059045269,169.56026885051585</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-46.56048350882859,169.55937956430276</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>-46.56042452321302,169.5584833135056</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>-46.56030586240593,169.55760618280607</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>-46.56016889844378,169.55673464004198</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-46.56005062921929,169.55585375487456</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>-46.55990393672711,169.55498009287868</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>-46.55980780822984,169.55409278481997</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>-46.559699392197125,169.55320879326993</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>-46.559586319617345,169.55231537791187</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>-46.559355266771526,169.55141908731682</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>-46.55937178633138,169.5504833748777</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>-46.55943842026313,169.54957069796987</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>-46.562283539182964,169.5625769230444</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>-46.56277096694736,169.5615452236526</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>-46.56098897763441,169.56107602150817</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-46.560594521001875,169.56026291902074</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-46.56044575180461,169.55938892327342</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-46.56039518623465,169.55849058570328</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-46.560286917516585,169.5576110690555</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>-46.56012884899402,169.55674541019556</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>-46.560048242449795,169.55585439900892</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>-46.559900842772215,169.55498092789844</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>-46.55981956523654,169.55408961162036</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>-46.55971945863018,169.55320337714883</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>-46.55961342902557,169.5523085565866</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>-46.55937407588346,169.55141548476175</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>-46.559376794954474,169.55048262349388</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>-46.55941623924663,169.54957402578654</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>-46.56224099581807,169.5625874671796</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>-46.56273205758349,169.56155486778383</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>-46.56098835721186,169.5610761752831</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-46.56059141889368,169.5602636879186</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-46.56040923562051,169.5593979746585</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>-46.560367533251274,169.55849744045565</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-46.560264254470944,169.5576169142835</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>-46.56009993912529,169.55675318466643</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>-46.56002808750716,169.55585983836332</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>-46.55988599178861,169.5549849359919</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>-46.55981735527289,169.55409020808656</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>-46.559723966947686,169.55320216031046</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>-46.55962848980762,169.5523047669582</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>-46.55938985414307,169.551412462711</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>-46.5593803725424,169.55048208679105</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>-46.55941078343206,169.5495748443216</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0545/nzd0545.xlsx
+++ b/data/nzd0545/nzd0545.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R462"/>
+  <dimension ref="A1:R463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28088,6 +28088,66 @@
       <c r="R462" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>448.98</v>
+      </c>
+      <c r="C463" t="n">
+        <v>514.0599999999999</v>
+      </c>
+      <c r="D463" t="n">
+        <v>327</v>
+      </c>
+      <c r="E463" t="n">
+        <v>290.13</v>
+      </c>
+      <c r="F463" t="n">
+        <v>278.36</v>
+      </c>
+      <c r="G463" t="n">
+        <v>284.45</v>
+      </c>
+      <c r="H463" t="n">
+        <v>283.12</v>
+      </c>
+      <c r="I463" t="n">
+        <v>273.57</v>
+      </c>
+      <c r="J463" t="n">
+        <v>273.37</v>
+      </c>
+      <c r="K463" t="n">
+        <v>269.72</v>
+      </c>
+      <c r="L463" t="n">
+        <v>276.1</v>
+      </c>
+      <c r="M463" t="n">
+        <v>276.25</v>
+      </c>
+      <c r="N463" t="n">
+        <v>276.28</v>
+      </c>
+      <c r="O463" t="n">
+        <v>258.77</v>
+      </c>
+      <c r="P463" t="n">
+        <v>262.97</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>271.41</v>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28102,7 +28162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33245,6 +33305,16 @@
       </c>
       <c r="B514" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>-1.1</v>
       </c>
     </row>
   </sheetData>
@@ -33413,28 +33483,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09827595283100453</v>
+        <v>-0.1016060786344113</v>
       </c>
       <c r="J2" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K2" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004416901788896865</v>
+        <v>0.004738087061389229</v>
       </c>
       <c r="M2" t="n">
-        <v>7.866866605894202</v>
+        <v>7.867328849988709</v>
       </c>
       <c r="N2" t="n">
-        <v>119.110149918712</v>
+        <v>118.9742779462759</v>
       </c>
       <c r="O2" t="n">
-        <v>10.9137596601131</v>
+        <v>10.90753308252035</v>
       </c>
       <c r="P2" t="n">
-        <v>459.1807965742273</v>
+        <v>459.2167359606165</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33491,28 +33561,28 @@
         <v>0.0386</v>
       </c>
       <c r="I3" t="n">
-        <v>2.137431521125991</v>
+        <v>2.13681332189688</v>
       </c>
       <c r="J3" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K3" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06582314943517853</v>
+        <v>0.06609148472359927</v>
       </c>
       <c r="M3" t="n">
-        <v>40.64119203132296</v>
+        <v>40.55641912600125</v>
       </c>
       <c r="N3" t="n">
-        <v>3516.481739880146</v>
+        <v>3508.740386139785</v>
       </c>
       <c r="O3" t="n">
-        <v>59.29993035308006</v>
+        <v>59.23462151596636</v>
       </c>
       <c r="P3" t="n">
-        <v>458.0986402619718</v>
+        <v>458.1053662487579</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33569,28 +33639,28 @@
         <v>0.028</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5453025876265697</v>
+        <v>-0.5375703476797312</v>
       </c>
       <c r="J4" t="n">
+        <v>462</v>
+      </c>
+      <c r="K4" t="n">
         <v>461</v>
       </c>
-      <c r="K4" t="n">
-        <v>460</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1040997760123759</v>
+        <v>0.1014812546824921</v>
       </c>
       <c r="M4" t="n">
-        <v>9.277128614856622</v>
+        <v>9.287891570971478</v>
       </c>
       <c r="N4" t="n">
-        <v>139.7686030738319</v>
+        <v>140.129502772785</v>
       </c>
       <c r="O4" t="n">
-        <v>11.82237721754098</v>
+        <v>11.8376307922145</v>
       </c>
       <c r="P4" t="n">
-        <v>324.073889203211</v>
+        <v>323.9904811852003</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33647,28 +33717,28 @@
         <v>0.0494</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3678462399541984</v>
+        <v>-0.3664965958703988</v>
       </c>
       <c r="J5" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K5" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05508727281608816</v>
+        <v>0.05495270766596794</v>
       </c>
       <c r="M5" t="n">
-        <v>8.589174594495386</v>
+        <v>8.578083814935049</v>
       </c>
       <c r="N5" t="n">
-        <v>126.6265444793412</v>
+        <v>126.3726525394617</v>
       </c>
       <c r="O5" t="n">
-        <v>11.25284606130117</v>
+        <v>11.24155916852559</v>
       </c>
       <c r="P5" t="n">
-        <v>296.9378921094058</v>
+        <v>296.9233348139006</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -33729,28 +33799,28 @@
         <v>0.0721</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4313172255007008</v>
+        <v>-0.4310994587560551</v>
       </c>
       <c r="J6" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K6" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05193421901805007</v>
+        <v>0.05212965547906667</v>
       </c>
       <c r="M6" t="n">
-        <v>10.61565332385541</v>
+        <v>10.59317909920325</v>
       </c>
       <c r="N6" t="n">
-        <v>180.5087863718879</v>
+        <v>180.1099374296179</v>
       </c>
       <c r="O6" t="n">
-        <v>13.43535583346745</v>
+        <v>13.42050436569423</v>
       </c>
       <c r="P6" t="n">
-        <v>289.4523151423577</v>
+        <v>289.4499134174424</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -33811,28 +33881,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08371940274674243</v>
+        <v>-0.08270943776141068</v>
       </c>
       <c r="J7" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K7" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00270242558860434</v>
+        <v>0.002650637672386713</v>
       </c>
       <c r="M7" t="n">
-        <v>9.245359822320657</v>
+        <v>9.229804758854719</v>
       </c>
       <c r="N7" t="n">
-        <v>138.8998718119863</v>
+        <v>138.6063302284255</v>
       </c>
       <c r="O7" t="n">
-        <v>11.78557897652832</v>
+        <v>11.77311896773432</v>
       </c>
       <c r="P7" t="n">
-        <v>284.4399184610237</v>
+        <v>284.4288749688505</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -33893,28 +33963,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01019613338832565</v>
+        <v>0.01088545977386834</v>
       </c>
       <c r="J8" t="n">
+        <v>462</v>
+      </c>
+      <c r="K8" t="n">
         <v>461</v>
       </c>
-      <c r="K8" t="n">
-        <v>460</v>
-      </c>
       <c r="L8" t="n">
-        <v>8.121131503691092e-05</v>
+        <v>9.301303319031451e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.231707854587031</v>
+        <v>6.221276955704319</v>
       </c>
       <c r="N8" t="n">
-        <v>69.46902452979215</v>
+        <v>69.32356116747715</v>
       </c>
       <c r="O8" t="n">
-        <v>8.334808007974278</v>
+        <v>8.326077177607541</v>
       </c>
       <c r="P8" t="n">
-        <v>281.2850185610583</v>
+        <v>281.2775543327475</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33975,28 +34045,28 @@
         <v>0.1322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0004041849670550115</v>
+        <v>8.836584719557153e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K9" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L9" t="n">
-        <v>1.199823710384962e-07</v>
+        <v>5.763120536350641e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>6.632333207151345</v>
+        <v>6.619495533741021</v>
       </c>
       <c r="N9" t="n">
-        <v>74.28386759485163</v>
+        <v>74.12418562470017</v>
       </c>
       <c r="O9" t="n">
-        <v>8.618808942937047</v>
+        <v>8.609540384056524</v>
       </c>
       <c r="P9" t="n">
-        <v>274.2797277135003</v>
+        <v>274.2831341465809</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -34057,28 +34127,28 @@
         <v>0.0518</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03839795989962191</v>
+        <v>0.04374719521454177</v>
       </c>
       <c r="J10" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K10" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003346478814647558</v>
+        <v>0.0004359236536445321</v>
       </c>
       <c r="M10" t="n">
-        <v>12.79504102683305</v>
+        <v>12.79819882099643</v>
       </c>
       <c r="N10" t="n">
-        <v>236.8749872600667</v>
+        <v>236.6706293235598</v>
       </c>
       <c r="O10" t="n">
-        <v>15.39074355773842</v>
+        <v>15.38410313679546</v>
       </c>
       <c r="P10" t="n">
-        <v>260.3464269696788</v>
+        <v>260.2881578910216</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34135,28 +34205,28 @@
         <v>0.027</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2557521147937718</v>
+        <v>-0.2502768522832905</v>
       </c>
       <c r="J11" t="n">
+        <v>462</v>
+      </c>
+      <c r="K11" t="n">
         <v>461</v>
       </c>
-      <c r="K11" t="n">
-        <v>460</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.01398261346748531</v>
+        <v>0.01344625212188011</v>
       </c>
       <c r="M11" t="n">
-        <v>13.25361339112683</v>
+        <v>13.25220301144597</v>
       </c>
       <c r="N11" t="n">
-        <v>249.721046243708</v>
+        <v>249.5079011648475</v>
       </c>
       <c r="O11" t="n">
-        <v>15.80256454641803</v>
+        <v>15.79581910395429</v>
       </c>
       <c r="P11" t="n">
-        <v>264.2268206692582</v>
+        <v>264.1674545583071</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34213,28 +34283,28 @@
         <v>0.0372</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0875290228297067</v>
+        <v>-0.07966836756399236</v>
       </c>
       <c r="J12" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K12" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0008191350778555817</v>
+        <v>0.000681174413920127</v>
       </c>
       <c r="M12" t="n">
-        <v>17.69782182191966</v>
+        <v>17.69321287075334</v>
       </c>
       <c r="N12" t="n">
-        <v>500.5238559141036</v>
+        <v>500.0957735264905</v>
       </c>
       <c r="O12" t="n">
-        <v>22.37239048278265</v>
+        <v>22.36282123361206</v>
       </c>
       <c r="P12" t="n">
-        <v>260.9235733738494</v>
+        <v>260.8375551038398</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34291,28 +34361,28 @@
         <v>0.0323</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6107759596681004</v>
+        <v>-0.6026301341602556</v>
       </c>
       <c r="J13" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K13" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05975865060069785</v>
+        <v>0.05841481404171278</v>
       </c>
       <c r="M13" t="n">
-        <v>13.35249724066434</v>
+        <v>13.35031212226793</v>
       </c>
       <c r="N13" t="n">
-        <v>314.3652051214377</v>
+        <v>314.3937565198477</v>
       </c>
       <c r="O13" t="n">
-        <v>17.7303470107451</v>
+        <v>17.73115214868587</v>
       </c>
       <c r="P13" t="n">
-        <v>274.4808028215086</v>
+        <v>274.3916639654847</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34369,28 +34439,28 @@
         <v>0.035</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1385704603564162</v>
+        <v>-0.1315439148003842</v>
       </c>
       <c r="J14" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K14" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003367286128370228</v>
+        <v>0.003045146786320729</v>
       </c>
       <c r="M14" t="n">
-        <v>13.5232033035407</v>
+        <v>13.52366719744298</v>
       </c>
       <c r="N14" t="n">
-        <v>306.0351109553362</v>
+        <v>305.9068344650481</v>
       </c>
       <c r="O14" t="n">
-        <v>17.49385923560997</v>
+        <v>17.4901925222408</v>
       </c>
       <c r="P14" t="n">
-        <v>264.2247336281575</v>
+        <v>264.1482445857197</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34447,28 +34517,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1977524081102274</v>
+        <v>-0.1957213966690555</v>
       </c>
       <c r="J15" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K15" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01723180079366415</v>
+        <v>0.01696125026846762</v>
       </c>
       <c r="M15" t="n">
-        <v>8.789884677946839</v>
+        <v>8.780329813439712</v>
       </c>
       <c r="N15" t="n">
-        <v>121.6790129996455</v>
+        <v>121.4613636050169</v>
       </c>
       <c r="O15" t="n">
-        <v>11.03082104830123</v>
+        <v>11.02095112070718</v>
       </c>
       <c r="P15" t="n">
-        <v>259.4590809679796</v>
+        <v>259.4371744267821</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34525,28 +34595,28 @@
         <v>0.0376</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.239413127278337</v>
+        <v>-0.2364071632876039</v>
       </c>
       <c r="J16" t="n">
+        <v>462</v>
+      </c>
+      <c r="K16" t="n">
         <v>461</v>
       </c>
-      <c r="K16" t="n">
-        <v>460</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.02430907244598945</v>
+        <v>0.02381242431076303</v>
       </c>
       <c r="M16" t="n">
-        <v>8.913816710831073</v>
+        <v>8.90859434726843</v>
       </c>
       <c r="N16" t="n">
-        <v>125.7369514584613</v>
+        <v>125.5646251546752</v>
       </c>
       <c r="O16" t="n">
-        <v>11.21324892519832</v>
+        <v>11.20556224179203</v>
       </c>
       <c r="P16" t="n">
-        <v>262.5669339568169</v>
+        <v>262.5345261622828</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34603,28 +34673,28 @@
         <v>0.0414</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3073089803969348</v>
+        <v>-0.3026550087640988</v>
       </c>
       <c r="J17" t="n">
+        <v>462</v>
+      </c>
+      <c r="K17" t="n">
         <v>461</v>
       </c>
-      <c r="K17" t="n">
-        <v>460</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.04169039933363716</v>
+        <v>0.04060029586443403</v>
       </c>
       <c r="M17" t="n">
-        <v>8.611865167187618</v>
+        <v>8.612872935308067</v>
       </c>
       <c r="N17" t="n">
-        <v>118.6433541278075</v>
+        <v>118.6267113064733</v>
       </c>
       <c r="O17" t="n">
-        <v>10.89235301153096</v>
+        <v>10.89158901659778</v>
       </c>
       <c r="P17" t="n">
-        <v>269.0820296233964</v>
+        <v>269.0318543861316</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34662,7 +34732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R462"/>
+  <dimension ref="A1:R463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76985,6 +77055,98 @@
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>-46.56224099581807,169.5625874671796</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>-46.56273205758349,169.56155486778383</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>-46.56098835721186,169.5610761752831</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-46.56057581972089,169.5602675543748</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-46.56038574826844,169.55940379653742</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-46.560353972653395,169.55850080191792</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-46.5602569066865,169.55761880941486</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>-46.56007907450998,169.55675879559385</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>-46.55998265048579,169.55587210075126</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>-46.55985567102971,169.5549931191752</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>-46.55981735527289,169.55409020808656</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>-46.559723966947686,169.55320216031046</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>-46.55962848980762,169.5523047669582</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>-46.55938985414307,169.551412462711</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>-46.5593803725424,169.55048208679105</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>-46.55941078343206,169.5495748443216</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
